--- a/datos/excel/reporte_2026-06-22.xlsx
+++ b/datos/excel/reporte_2026-06-22.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,51 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>19:26:11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-19.35</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>726.6 Hz | 1093.8 Hz | 1460.9 Hz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2525</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11423</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-06-22.xlsx
+++ b/datos/excel/reporte_2026-06-22.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,51 @@
         <v>11423</v>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19:27:25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1945.3 Hz</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2507</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11465</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
         </is>
